--- a/birthday-reader/data/employees.xlsx
+++ b/birthday-reader/data/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Birthday-Mail\birthday-reader\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F1BB9-CFBA-4F9C-9693-717E81957083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C043403D-44F9-457B-B79B-9BD1381A4E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1120" windowWidth="15380" windowHeight="8750" xr2:uid="{34D36F85-5268-4715-9CA8-69230E014947}"/>
   </bookViews>
@@ -153,7 +153,7 @@
     <t>13/05/2001</t>
   </si>
   <si>
-    <t>18/05/2000</t>
+    <t>19/05/2000</t>
   </si>
 </sst>
 </file>

--- a/birthday-reader/data/employees.xlsx
+++ b/birthday-reader/data/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Birthday-Mail\birthday-reader\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C043403D-44F9-457B-B79B-9BD1381A4E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEC418-4F73-4FBE-B39E-549317E2C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1120" windowWidth="15380" windowHeight="8750" xr2:uid="{34D36F85-5268-4715-9CA8-69230E014947}"/>
   </bookViews>
@@ -153,7 +153,7 @@
     <t>13/05/2001</t>
   </si>
   <si>
-    <t>19/05/2000</t>
+    <t>01/06/2000</t>
   </si>
 </sst>
 </file>

--- a/birthday-reader/data/employees.xlsx
+++ b/birthday-reader/data/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Birthday-Mail\birthday-reader\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EEC418-4F73-4FBE-B39E-549317E2C25E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E17557D-6132-41B7-A96B-9FDA08C2FCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1120" windowWidth="15380" windowHeight="8750" xr2:uid="{34D36F85-5268-4715-9CA8-69230E014947}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Department</t>
   </si>
   <si>
-    <t>Position</t>
-  </si>
-  <si>
     <t>John Doe</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t xml:space="preserve">Sales </t>
   </si>
   <si>
-    <t>Manager</t>
-  </si>
-  <si>
     <t>Bob Johnson</t>
   </si>
   <si>
@@ -84,18 +78,12 @@
     <t>IT</t>
   </si>
   <si>
-    <t>Developer</t>
-  </si>
-  <si>
     <t>bob.johnson@company.com</t>
   </si>
   <si>
     <t>HR</t>
   </si>
   <si>
-    <t>Specialist</t>
-  </si>
-  <si>
     <t>Alice Williams</t>
   </si>
   <si>
@@ -108,18 +96,12 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Analyst</t>
-  </si>
-  <si>
     <t>Charlie Brown</t>
   </si>
   <si>
     <t>Operations</t>
   </si>
   <si>
-    <t>Coordinator</t>
-  </si>
-  <si>
     <t>charlie.b@company.com</t>
   </si>
   <si>
@@ -129,9 +111,6 @@
     <t>DOB</t>
   </si>
   <si>
-    <t>imagePath</t>
-  </si>
-  <si>
     <t>Quốc Anh</t>
   </si>
   <si>
@@ -153,7 +132,7 @@
     <t>13/05/2001</t>
   </si>
   <si>
-    <t>01/06/2000</t>
+    <t>22/06/2000</t>
   </si>
 </sst>
 </file>
@@ -566,133 +545,119 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -700,16 +665,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">

--- a/birthday-reader/data/employees.xlsx
+++ b/birthday-reader/data/employees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Birthday-Mail\birthday-reader\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E17557D-6132-41B7-A96B-9FDA08C2FCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7A14BD-3EBA-47B7-A453-21EBC5DE45F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1120" windowWidth="15380" windowHeight="8750" xr2:uid="{34D36F85-5268-4715-9CA8-69230E014947}"/>
   </bookViews>
